--- a/competitor_feeds.xlsx
+++ b/competitor_feeds.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Легенда" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'competitor_feeds'!$A$1:$L$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'competitor_feeds'!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -536,6 +536,7 @@
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,6 +600,11 @@
           <t>Дата проверки</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>id в реестре</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -657,6 +663,11 @@
           <t>14.10.2026</t>
         </is>
       </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>kts_vacancies</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -666,7 +677,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Сайт: статьи, кейсы, страницы</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -681,36 +692,49 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>Sitemap (urlset)</t>
+          <t>Sitemap (urlset), целиком</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Проверено 13.10.2026</t>
+          <t>Проверено 15.10.2026</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
+          <t>Карта сайта забирается целиком, сигнал — по пути; правила в sources.yaml</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>RSS нет. Статьи — URL с /posts/ и /cases/; lastmod нет, новые определять по появлению URL</t>
-        </is>
-      </c>
-      <c r="K3" s="10" t="inlineStr"/>
-      <c r="L3" s="10" t="inlineStr"/>
+          <t>/posts/ → статья, /cases/ → кейс, остальные разделы (proptech, hrtech, finops, devops, wolfram-wfm, solutions…) → новая страница, /awards/ — шум. lastmod есть только у кейсов. Замер 15.10: 149 URL — posts 105, cases 15, ~15 страниц направлений</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>ОК: карта отдаётся целиком, разделы посчитаны</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>kts_site</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -760,7 +784,7 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>Часть статей KTS выходит только на Хабре; по паспорту сторонние площадки остаются в сводке</t>
+          <t>Часть статей KTS выходит только на Хабре; по паспорту сторонние площадки остаются в сводке. Замер 15.10: 4 статьи за 90 дней; 2 из 40 совместно с Альфа-Банком</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
@@ -771,6 +795,11 @@
       <c r="L4" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>kts_blog_habr</t>
         </is>
       </c>
     </row>
@@ -831,6 +860,11 @@
           <t>14.10.2026</t>
         </is>
       </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>napoleonit_vacancies</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -840,7 +874,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Сайт: статьи, кейсы, страницы</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -855,36 +889,49 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>Sitemap index → sitemap-0.xml</t>
+          <t>Sitemap index → sitemap-0.xml, целиком</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Проверено 13.10.2026</t>
+          <t>Проверено 15.10.2026</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
+          <t>Карта сайта забирается целиком, сигнал — по пути; правила в sources.yaml</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>RSS нет; /sitemap.xml → 404, реальная карта из robots.txt. Фильтр URL: /blog/. Даты — на странице /blog. Блога на Хабре по слагам napoleonit / napoleon-it не найдено (404), слаг мог не совпасть</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr"/>
+          <t>/blog/ → статья, /cases/ и /stories/ → кейс, solutions, industries, services → новая страница. lastmod нет ни у одного URL — событие датируется моментом обнаружения. /sitemap.xml → 404, карта из robots.txt. Замер 15.10: 340 URL — blog 271, cases 27, solutions 10, industries 8, stories 8, services 6</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>ОК: карта отдаётся целиком, разделы посчитаны</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>napoleonit_site</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -943,6 +990,11 @@
           <t>14.10.2026</t>
         </is>
       </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>rmr_vacancies</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -992,7 +1044,7 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>Своего сайта фактически нет: redmadrobot.ru не отвечает (ERR_CONNECTION_CLOSED), redmadrobot.com/articles не отрисовывает список (их бэкенд отдаёт 500), sitemap.xml отсутствует</t>
+          <t>Своего сайта фактически нет: redmadrobot.ru не отвечает (ERR_CONNECTION_CLOSED), redmadrobot.com/articles не отрисовывает список (их бэкенд отдаёт 500), sitemap.xml отсутствует. Замер 15.10: 0 статей за 90 дней, 13 за год</t>
         </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
@@ -1003,6 +1055,11 @@
       <c r="L8" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>rmr_blog_habr</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1111,7 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Запасной источник вакансий: careers.just-ai.com</t>
+          <t>Белого запасного источника нет: careers.just-ai.com — HTML-страница</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
@@ -1065,6 +1122,11 @@
       <c r="L9" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>justai_vacancies</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1138,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Сайт: статьи, кейсы, страницы</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1086,41 +1148,54 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>https://just-ai.com/blog-sitemap.xml</t>
+          <t>https://just-ai.com/sitemap.xml</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Sitemap (urlset, lastmod)</t>
+          <t>Sitemap index → 5 дочерних карт</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Проверено 13.10.2026</t>
+          <t>Проверено 15.10.2026</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
+          <t>Индекс карт сайта; тип страницы — по дочерней карте, правила в sources.yaml</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>RSS /feed/ и /blog/feed пустые. lastmod = дата изменения, не публикации. Блога на Хабре по слагам justai / just-ai не найдено (404), слаг мог не совпасть</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr"/>
-      <c r="L10" s="10" t="inlineStr"/>
+          <t>blog → статья, case → кейс, page и solutions → новая страница, category → шум. Страницы мероприятий режутся по slug. lastmod у страниц — грубый сигнал «страница обновлена». Замер 15.10: блог 187, кейсы 26 (3 новых за 90 дней), страницы 45 (12 изменены за 90 дней). RSS /feed/ и /blog/feed пустые</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>ОК: индекс и все 5 дочерних карт отдаются</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>justai_site</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1165,7 +1240,7 @@
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Запасной источник — страница https://siberian.pro/vakansii/ на сайте компании</t>
+          <t>Белого запасного нет: /vakansii/ — HTML-страница и отстаёт от реальности</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
@@ -1181,6 +1256,11 @@
       <c r="L11" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>siberian_vacancies</t>
         </is>
       </c>
     </row>
@@ -1232,11 +1312,16 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Последняя запись 08.10.2026. description/content пустые — берём title, link, pubDate, category; текст со страницы статьи</t>
+          <t>WordPress. Берём title, link, pubDate, category; текст статьи не забираем. ФИЛЬТР: еженедельные «Главные новости AI: дайджест» режутся по заголовку и адресу — это пересказ рынка под именем компании, 4 из 10 последних записей. Замер 15.10: 10 записей за 5 недель, 6 из 10 в категории «Новости»</t>
         </is>
       </c>
       <c r="K12" s="10" t="inlineStr"/>
       <c r="L12" s="10" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>siberian_blog</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1286,7 +1371,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Запасной источник вакансий: https://www.simbirsoft.com/vacancies/ (страница работает)</t>
+          <t>Белого запасного источника нет: simbirsoft.com/vacancies/ — HTML-страница</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
@@ -1297,6 +1382,11 @@
       <c r="L13" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>simbirsoft_vacancies</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1438,7 @@
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Основной источник статей SimbirSoft: в ленте есть даты, в отличие от листинга на сайте</t>
+          <t>Основной источник статей SimbirSoft: в ленте есть даты, в отличие от листинга на сайте. Замер 15.10: 5 статей за 90 дней. Единственный белый источник статей SimbirSoft</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
@@ -1359,75 +1449,85 @@
       <c r="L14" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>simbirsoft_blog_habr</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>SimbirSoft</t>
+          <t>Softline digital</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Блог (сайт, запасной)</t>
+          <t>Вакансии</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>https://www.simbirsoft.com/blog/</t>
+          <t>https://hh.ru/employer/2381</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>https://www.simbirsoft.com/blog/tag/</t>
+          <t>https://api.hh.ru/vacancies?employer_id=2381</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>HTML-листинг (запасной)</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Проверено 14.10.2026</t>
+          <t>JSON (API hh.ru)</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Кандидат (id ведёт на группу)</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Адрес /blog/tag/ был догадкой — подтвердился</t>
+          <t>Шаблон официального API hh.ru; employer_id взят из исходной ссылки</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Запрос с токеном приложения отдаёт JSON: found ≈ числу вакансий на вкладке hh.ru, items[].employer.name = нужной компании</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Пока нет токена: открыть https://hh.ru/employer/&lt;id&gt; в браузере и сверить название компании — это проверяет главное и от API не зависит</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>RSS /blog/rss/ → 404. Sitemap заявлен в robots.txt, но даёт 404 и в браузере — строка про sitemap убрана</t>
+          <t>Работодатель 2381 называется просто «Softline» — это вся группа. Отдельного работодателя «Softline digital» в каталоге hh.ru нет: по запросу Softline найдено 20 компаний, среди них подходящей нет. ИИ-вакансии придётся отбирать из общего потока группы по тексту. Белого источника статей по Softline digital нет: листинг блога — только через вёрстку, карта сайта устарела (3 из 12 свежих статей), Хабр мёртв с 2022. См. sources.yaml: coverage_gaps</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>ОК: /blog/tag/ отдаёт все статьи карточками. Нужен, только если лента Хабра не покроет темы</t>
+          <t>id проверен 14.10.2026: на hh.ru/employer/2381 значится «Softline», НЕ Softline digital. Подозрение подтвердилось. Сама лента — 403 без токена</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>softline_vacancies</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Softline digital</t>
+          <t>AGIMA</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1437,12 +1537,12 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>https://hh.ru/employer/2381</t>
+          <t>https://hh.ru/employer/238354</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>https://api.hh.ru/vacancies?employer_id=2381</t>
+          <t>https://api.hh.ru/vacancies?employer_id=238354</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1452,7 +1552,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Кандидат (id ведёт на группу)</t>
+          <t>Кандидат (id подтверждён)</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1472,44 +1572,49 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Работодатель 2381 называется просто «Softline» — это вся группа. Отдельного работодателя «Softline digital» в каталоге hh.ru нет: по запросу Softline найдено 20 компаний, среди них подходящей нет. ИИ-вакансии придётся отбирать из общего потока группы по тексту</t>
+          <t>Запасной белый источник: новые URL в /careers/ из карты сайта agima.ru (16 на 15.10)</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>id проверен 14.10.2026: на hh.ru/employer/2381 значится «Softline», НЕ Softline digital. Подозрение подтвердилось. Сама лента — 403 без токена</t>
+          <t>id подтверждён 14.10.2026: на hh.ru/employer/238354 значится «AGIMA». Сама лента — 403 forbidden без токена, приложение на dev.hh.ru на модерации</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>agima_vacancies</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Softline digital</t>
+          <t>AGIMA</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Блог (Хабр)</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>https://softline.ru/about/blog</t>
+          <t>https://habr.com/ru/companies/agima/articles/</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>https://softline.ru/about/blog</t>
+          <t>https://habr.com/ru/rss/companies/agima/articles/</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>HTML-листинг</t>
+          <t>RSS (Хабр)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -1519,7 +1624,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Параметр NEWS_COUNT (компонент новостей Битрикса) оказался догадкой и не подтвердился — убран</t>
+          <t>Шаблон RSS Хабра habr.com/ru/rss/companies/&lt;слаг&gt;/articles/ — подтверждён на трёх компаниях</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -1529,22 +1634,27 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Если у Softline digital найдётся свой раздел или сайт — заменить источник целиком</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Открытый вопрос паспорта: какой сайт/раздел Softline digital отслеживать. Sitemap Bitrix не обновляется (lastmod 27.03.2026). Блог на Хабре мёртв — последняя запись 25.02.2022</t>
+          <t>Самый активный источник в карте: пишут профильное (LLM, агентские контуры). Замер 15.10: 10 статей за 90 дней; 2 из 40 совместные — Ozon Банк, Онтико</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>ОК с оговоркой: ?NEWS_COUNT=10 тоже отдаёт 40 карточек, параметр игнорируется — берём голый адрес, 40 записей на странице хватает. Статьи про ИИ есть, но блог общегрупповой</t>
+          <t>ОК: XML, 40 записей, последняя 14.10.2026 — день проверки</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>agima_blog_habr</t>
         </is>
       </c>
     </row>
@@ -1556,151 +1666,161 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Вакансии</t>
+          <t>Сайт: статьи, кейсы, страницы</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>https://hh.ru/employer/238354</t>
+          <t>https://www.agima.ru/blog/</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>https://api.hh.ru/vacancies?employer_id=238354</t>
+          <t>https://www.agima.ru/sitemap.xml</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>JSON (API hh.ru)</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Кандидат (id подтверждён)</t>
+          <t>Sitemap (urlset, lastmod), целиком</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Проверено 15.10.2026</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Шаблон официального API hh.ru; employer_id взят из исходной ссылки</t>
+          <t>Карта сайта забирается целиком, сигнал — по пути; правила в sources.yaml</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Запрос с токеном приложения отдаёт JSON: found ≈ числу вакансий на вкладке hh.ru, items[].employer.name = нужной компании</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Пока нет токена: открыть https://hh.ru/employer/&lt;id&gt; в браузере и сверить название компании — это проверяет главное и от API не зависит</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>Запасной источник вакансий: /careers/vacancy/ в sitemap agima.ru</t>
+          <t>/blog/ → статья, /projects/ → кейс, approach и special-projects → новая страница; glossary, authors, events, careers — шум. lastmod у страниц — «страница обновлена». Замер 15.10: 1107 URL — glossary 531, blog 259, projects 137, authors 97, events 43</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>id подтверждён 14.10.2026: на hh.ru/employer/238354 значится «AGIMA». Сама лента — 403 forbidden без токена, приложение на dev.hh.ru на модерации</t>
+          <t>ОК: карта отдаётся целиком, разделы посчитаны</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>14.10.2026</t>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>agima_site</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>AGIMA</t>
+          <t>R77 AI</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Блог (Хабр)</t>
+          <t>Вакансии</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>https://habr.com/ru/companies/agima/articles/</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>https://habr.com/ru/rss/companies/agima/articles/</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>RSS (Хабр)</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Проверено 14.10.2026</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Нет источника (проверено)</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Шаблон RSS Хабра habr.com/ru/rss/companies/&lt;слаг&gt;/articles/ — подтверждён на трёх компаниях</t>
+          <t>Адреса нет</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Перепроверять раз в пару месяцев: компания основана в 2024, может появиться на hh.ru позже</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Пометить «источника нет» и принять как дыру</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Самый активный источник в карте: пишут профильное (LLM, агентские контуры)</t>
+          <t>Блога на Хабре по слагам r77 / r77ai не найдено (404), слаг мог не совпасть</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>ОК: XML, 40 записей, последняя 14.10.2026 — день проверки</t>
+          <t>Поиск в каталоге hh.ru 14.10.2026: по «R77» и «R77 AI» — 0 компаний; по «Р77» — ООО Р-77 (Чебоксары, без описания, 0 вакансий), это другая компания. На hh.ru R77 AI нет — дыра остаётся</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>r77_vacancies</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>AGIMA</t>
+          <t>R77 AI</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Блог (сайт)</t>
+          <t>Кейсы</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>https://www.agima.ru/blog/</t>
+          <t>https://r77.ai/media</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>https://www.agima.ru/sitemap.xml</t>
+          <t>https://r77.ai/rss-feed-599747680771.xml</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Sitemap (urlset, lastmod)</t>
+          <t>RSS Tilda</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Проверено 13.10.2026</t>
+          <t>Проверено 13.10.2026 (спящий)</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1710,26 +1830,39 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Раз в пару месяцев — не ожил ли источник</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Если и через полгода тишина — убрать R77 AI из карты и записать как дыру</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>RSS нет. Статьи /blog/&lt;рубрика&gt;/&lt;slug&gt;/. Sitemap большой (глоссарий, авторы) — фильтр по /blog/</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr"/>
-      <c r="L20" s="10" t="inlineStr"/>
+          <t>Единственный белый источник R77 AI. Компания выкладывает кейсы пачками. Tilda: элементы &lt;item turbo="true"&gt;; у каждого кейса &lt;category&gt; — отрасль клиента. Замер 15.10: 28 кейсов — 2024: 10, 2025: 16, 2026: 2 (обе 15.06 одним днём)</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>Лента рабочая, но компания почти не публикует. Держим как спящий источник: запрос раз в неделю ничего не стоит</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>r77_cases</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>R77 AI</t>
+          <t>Nord Clan</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1739,74 +1872,75 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>https://hh.ru/employer/4105707</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://api.hh.ru/vacancies?employer_id=4105707</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>Нет источника (проверено)</t>
+          <t>JSON (API hh.ru)</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Кандидат (id подтверждён)</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Адреса нет</t>
+          <t>Шаблон официального API hh.ru; employer_id взят из исходной ссылки</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Перепроверять раз в пару месяцев: компания основана в 2024, может появиться на hh.ru позже</t>
+          <t>Запрос с токеном приложения отдаёт JSON: found ≈ числу вакансий на вкладке hh.ru, items[].employer.name = нужной компании</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Пометить «источника нет» и принять как дыру</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Блога на Хабре по слагам r77 / r77ai не найдено (404), слаг мог не совпасть</t>
-        </is>
-      </c>
+          <t>Пока нет токена: открыть https://hh.ru/employer/&lt;id&gt; в браузере и сверить название компании — это проверяет главное и от API не зависит</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr"/>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>Поиск в каталоге hh.ru 14.10.2026: по «R77» и «R77 AI» — 0 компаний; по «Р77» — ООО Р-77 (Чебоксары, без описания, 0 вакансий), это другая компания. На hh.ru R77 AI нет — дыра остаётся</t>
+          <t>id подтверждён 14.10.2026: на hh.ru/employer/4105707 значится «Норд Клан». Сама лента — 403 forbidden без токена, приложение на dev.hh.ru на модерации</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
           <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>nordclan_vacancies</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>R77 AI</t>
+          <t>Nord Clan</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Кейсы</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>https://r77.ai/media</t>
+          <t>https://nordclan.com/blog</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>https://r77.ai/rss-feed-599747680771.xml</t>
+          <t>https://nordclan.com/rss-feed-111193114321.xml</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -1816,154 +1950,47 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Проверено 13.10.2026 (спящий)</t>
+          <t>Проверено 15.10.2026</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
+          <t>id ленты — из sitemap-feeds.xml; адрес RSS по шаблону Tilda — подтверждён</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>Раз в пару месяцев — не ожил ли источник</t>
-        </is>
-      </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Если и через полгода тишина — убрать R77 AI из карты и записать как дыру</t>
+          <t>Использовать проверенный https://nordclan.com/sitemap-feed-111193114321.xml (≈49 статей), новые — по появлению URL</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Единственная оставленная лента R77: две ленты публикаций (/tpost/) убраны 14.10.2026 — последние записи больше года назад. Индекс лент: https://r77.ai/sitemap-feeds.xml</t>
+          <t>Единственный живой источник Nord Clan. Много SEO-обзоров рынка («ТОП-8 российских RAG-систем») — громкость гасится лимитом 3 статьи на компанию в сводке. Tilda: элементы &lt;item turbo="true"&gt;. Замер 15.10: 24 записи за 90 дней</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>Лента рабочая, но компания почти не публикует. Держим как спящий источник: запрос раз в неделю ничего не стоит</t>
+          <t>ОК: XML, 50 записей, все в /blog/, последняя 14.10.2026</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>14.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Nord Clan</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Вакансии</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>https://hh.ru/employer/4105707</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>https://api.hh.ru/vacancies?employer_id=4105707</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>JSON (API hh.ru)</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Кандидат (id подтверждён)</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Шаблон официального API hh.ru; employer_id взят из исходной ссылки</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Запрос с токеном приложения отдаёт JSON: found ≈ числу вакансий на вкладке hh.ru, items[].employer.name = нужной компании</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Пока нет токена: открыть https://hh.ru/employer/&lt;id&gt; в браузере и сверить название компании — это проверяет главное и от API не зависит</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>id подтверждён 14.10.2026: на hh.ru/employer/4105707 значится «Норд Клан». Сама лента — 403 forbidden без токена, приложение на dev.hh.ru на модерации</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>14.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Nord Clan</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Блог</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>https://nordclan.com/blog</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>https://nordclan.com/rss-feed-111193114321.xml</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>RSS Tilda</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Кандидат (частично)</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>id ленты — факт (sitemap-feed проверен); адрес RSS — шаблон Tilda, подтверждён на двух других лентах</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>Открывается как RSS; ссылки на /blog/; последняя запись 12.10.2026 или свежее</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Использовать проверенный https://nordclan.com/sitemap-feed-111193114321.xml (≈49 статей), новые — по появлению URL</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>Единственный живой источник у Nord Clan: лента новостей убрана 14.10.2026, блог на Хабре мёртв (последняя запись 30.09.2024). Индекс лент: https://nordclan.com/sitemap-feeds.xml</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr"/>
-      <c r="L24" s="13" t="inlineStr"/>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>nordclan_blog</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L24"/>
+  <autoFilter ref="A1:M22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1974,7 +2001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2284,102 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>ПРАВКА 15.10.2026</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Синхронизация с реестром после технической рецензии</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Колонка «id в реестре»</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Связь строки с sources.yaml. Таблица — для чтения глазами; при расхождении верен реестр</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Убраны 2 строки html_list</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Блог Softline и запасной листинг SimbirSoft — оба требовали разбора вёрстки, это вне правил проекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Карты сайтов — целиком</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>4 строки «Сайт»: KTS, Napoleon IT, Just AI, AGIMA. Кроме статей теперь ловятся кейсы и новые страницы услуг — данные и раньше скачивались, их отрезал фильтр /blog/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Nord Clan проверен</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Лента блога работает: 50 записей, последняя 14.10. Кандидатов в таблице больше нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Фильтр дайджестов Siberian.pro</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Еженедельные «Главные новости AI» — пересказ рынка под именем компании, режутся</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Запасные источники вакансий</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>HTML-страницы вакансий Just AI, SimbirSoft, Siberian.pro убраны; у AGIMA запасной теперь белый — /careers/ в карте сайта</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Дыры: белых источников нет</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Softline digital — ни одного по компании; R77 AI — практически ничего; red_mad_robot — только вакансии после токена; Telegram — ни по кому. Подробно: sources.yaml → coverage_gaps, BACKLOG.md → раздел 3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
